--- a/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 4.xlsx
+++ b/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 4.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Tiketing 4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Tiketing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85197B0C-A75A-4A4B-ACBB-15A5E65384D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Soal!$A$1:$H$9</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -174,7 +173,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -322,13 +321,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -646,7 +645,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -690,11 +689,11 @@
       <c r="I1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
@@ -706,11 +705,26 @@
       <c r="C2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="16"/>
+      <c r="D2" s="16" t="str">
+        <f>HLOOKUP(LEFT(C2,3),$A$12:$D$13,2,FALSE)</f>
+        <v>Bisnis</v>
+      </c>
+      <c r="E2" s="16" t="str">
+        <f>VLOOKUP(RIGHT(C2,1),$A$16:$E$19,2,FALSE)</f>
+        <v>Anak</v>
+      </c>
+      <c r="F2" s="17">
+        <f>INDEX($B$16:$E$19,MATCH(E2,$B$16:$B$19,0),MATCH(D2,$B$16:$E$16,0))</f>
+        <v>50000</v>
+      </c>
+      <c r="G2" s="18">
+        <f>IF(AND(D2="Executive",E2="Anak"),F2*0.1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="16">
+        <f>F2-G2</f>
+        <v>50000</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
@@ -722,11 +736,26 @@
       <c r="C3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="16"/>
+      <c r="D3" s="16" t="str">
+        <f t="shared" ref="D3:D9" si="0">HLOOKUP(LEFT(C3,3),$A$12:$D$13,2,FALSE)</f>
+        <v>Ekonomi</v>
+      </c>
+      <c r="E3" s="16" t="str">
+        <f t="shared" ref="E3:E9" si="1">VLOOKUP(RIGHT(C3,1),$A$16:$E$19,2,FALSE)</f>
+        <v>Dewasa</v>
+      </c>
+      <c r="F3" s="17">
+        <f t="shared" ref="F3:F9" si="2">INDEX($B$16:$E$19,MATCH(E3,$B$16:$B$19,0),MATCH(D3,$B$16:$E$16,0))</f>
+        <v>50000</v>
+      </c>
+      <c r="G3" s="18">
+        <f t="shared" ref="G3:G9" si="3">IF(AND(D3="Executive",E3="Anak"),F3*0.1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="16">
+        <f t="shared" ref="H3:H9" si="4">F3-G3</f>
+        <v>50000</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
@@ -738,11 +767,26 @@
       <c r="C4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="16"/>
+      <c r="D4" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Executive</v>
+      </c>
+      <c r="E4" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Anak</v>
+      </c>
+      <c r="F4" s="17">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="G4" s="18">
+        <f t="shared" si="3"/>
+        <v>10000</v>
+      </c>
+      <c r="H4" s="16">
+        <f t="shared" si="4"/>
+        <v>90000</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
@@ -754,11 +798,26 @@
       <c r="C5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="16"/>
+      <c r="D5" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Executive</v>
+      </c>
+      <c r="E5" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Dewasa</v>
+      </c>
+      <c r="F5" s="17">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
@@ -770,11 +829,26 @@
       <c r="C6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="16"/>
+      <c r="D6" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Ekonomi</v>
+      </c>
+      <c r="E6" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Lansia</v>
+      </c>
+      <c r="F6" s="17">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="G6" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="16">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -786,11 +860,26 @@
       <c r="C7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="16"/>
+      <c r="D7" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Bisnis</v>
+      </c>
+      <c r="E7" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Dewasa</v>
+      </c>
+      <c r="F7" s="17">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="G7" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
@@ -802,11 +891,26 @@
       <c r="C8" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="16"/>
+      <c r="D8" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Ekonomi</v>
+      </c>
+      <c r="E8" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Anak</v>
+      </c>
+      <c r="F8" s="17">
+        <f t="shared" si="2"/>
+        <v>25000</v>
+      </c>
+      <c r="G8" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <f t="shared" si="4"/>
+        <v>25000</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
@@ -818,11 +922,26 @@
       <c r="C9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="16"/>
+      <c r="D9" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Executive</v>
+      </c>
+      <c r="E9" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Lansia</v>
+      </c>
+      <c r="F9" s="17">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+      <c r="G9" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="16">
+        <f t="shared" si="4"/>
+        <v>300000</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -864,27 +983,27 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="G15" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
@@ -902,14 +1021,14 @@
       <c r="E16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -927,14 +1046,14 @@
       <c r="E17" s="6">
         <v>100000</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -952,14 +1071,14 @@
       <c r="E18" s="6">
         <v>200000</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -977,12 +1096,12 @@
       <c r="E19" s="6">
         <v>300000</v>
       </c>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -995,7 +1114,7 @@
     <mergeCell ref="G18:L18"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J1" r:id="rId1" xr:uid="{22D60958-41B8-4FD3-B667-332BD6F81199}"/>
+    <hyperlink ref="J1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 4.xlsx
+++ b/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 4.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Tiketing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Tiketing 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85197B0C-A75A-4A4B-ACBB-15A5E65384D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Soal!$A$1:$H$9</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -173,7 +174,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -321,13 +322,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -645,7 +646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -689,11 +690,11 @@
       <c r="I1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
@@ -705,26 +706,11 @@
       <c r="C2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="16" t="str">
-        <f>HLOOKUP(LEFT(C2,3),$A$12:$D$13,2,FALSE)</f>
-        <v>Bisnis</v>
-      </c>
-      <c r="E2" s="16" t="str">
-        <f>VLOOKUP(RIGHT(C2,1),$A$16:$E$19,2,FALSE)</f>
-        <v>Anak</v>
-      </c>
-      <c r="F2" s="17">
-        <f>INDEX($B$16:$E$19,MATCH(E2,$B$16:$B$19,0),MATCH(D2,$B$16:$E$16,0))</f>
-        <v>50000</v>
-      </c>
-      <c r="G2" s="18">
-        <f>IF(AND(D2="Executive",E2="Anak"),F2*0.1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="16">
-        <f>F2-G2</f>
-        <v>50000</v>
-      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
@@ -736,26 +722,11 @@
       <c r="C3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="16" t="str">
-        <f t="shared" ref="D3:D9" si="0">HLOOKUP(LEFT(C3,3),$A$12:$D$13,2,FALSE)</f>
-        <v>Ekonomi</v>
-      </c>
-      <c r="E3" s="16" t="str">
-        <f t="shared" ref="E3:E9" si="1">VLOOKUP(RIGHT(C3,1),$A$16:$E$19,2,FALSE)</f>
-        <v>Dewasa</v>
-      </c>
-      <c r="F3" s="17">
-        <f t="shared" ref="F3:F9" si="2">INDEX($B$16:$E$19,MATCH(E3,$B$16:$B$19,0),MATCH(D3,$B$16:$E$16,0))</f>
-        <v>50000</v>
-      </c>
-      <c r="G3" s="18">
-        <f t="shared" ref="G3:G9" si="3">IF(AND(D3="Executive",E3="Anak"),F3*0.1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="16">
-        <f t="shared" ref="H3:H9" si="4">F3-G3</f>
-        <v>50000</v>
-      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
@@ -767,26 +738,11 @@
       <c r="C4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Executive</v>
-      </c>
-      <c r="E4" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Anak</v>
-      </c>
-      <c r="F4" s="17">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="G4" s="18">
-        <f t="shared" si="3"/>
-        <v>10000</v>
-      </c>
-      <c r="H4" s="16">
-        <f t="shared" si="4"/>
-        <v>90000</v>
-      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
@@ -798,26 +754,11 @@
       <c r="C5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Executive</v>
-      </c>
-      <c r="E5" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Dewasa</v>
-      </c>
-      <c r="F5" s="17">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-      <c r="G5" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="16">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
@@ -829,26 +770,11 @@
       <c r="C6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Ekonomi</v>
-      </c>
-      <c r="E6" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Lansia</v>
-      </c>
-      <c r="F6" s="17">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="G6" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="16">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -860,26 +786,11 @@
       <c r="C7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Bisnis</v>
-      </c>
-      <c r="E7" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Dewasa</v>
-      </c>
-      <c r="F7" s="17">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="G7" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="16">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
@@ -891,26 +802,11 @@
       <c r="C8" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Ekonomi</v>
-      </c>
-      <c r="E8" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Anak</v>
-      </c>
-      <c r="F8" s="17">
-        <f t="shared" si="2"/>
-        <v>25000</v>
-      </c>
-      <c r="G8" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="16">
-        <f t="shared" si="4"/>
-        <v>25000</v>
-      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
@@ -922,26 +818,11 @@
       <c r="C9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Executive</v>
-      </c>
-      <c r="E9" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Lansia</v>
-      </c>
-      <c r="F9" s="17">
-        <f t="shared" si="2"/>
-        <v>300000</v>
-      </c>
-      <c r="G9" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="16">
-        <f t="shared" si="4"/>
-        <v>300000</v>
-      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -983,27 +864,27 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
@@ -1021,14 +902,14 @@
       <c r="E16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1046,14 +927,14 @@
       <c r="E17" s="6">
         <v>100000</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1071,14 +952,14 @@
       <c r="E18" s="6">
         <v>200000</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1096,12 +977,12 @@
       <c r="E19" s="6">
         <v>300000</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1114,7 +995,7 @@
     <mergeCell ref="G18:L18"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J1" r:id="rId1"/>
+    <hyperlink ref="J1" r:id="rId1" xr:uid="{22D60958-41B8-4FD3-B667-332BD6F81199}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
